--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4023325834933801</v>
+        <v>0.398223309657814</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03968560193011214</v>
+        <v>0.0392698381059611</v>
       </c>
       <c r="E2" t="n">
-        <v>0.324550233005567</v>
+        <v>0.3212558412914116</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4801149339811931</v>
+        <v>0.4751907780242164</v>
       </c>
       <c r="G2" t="n">
-        <v>3.746968690837363e-24</v>
+        <v>3.645104327879786e-24</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4818619666291217</v>
+        <v>0.4740212656916218</v>
       </c>
       <c r="I2" t="n">
-        <v>12.03568730726128</v>
+        <v>11.8520500782549</v>
       </c>
       <c r="J2" t="n">
-        <v>3.789464853375086</v>
+        <v>3.783304057116402</v>
       </c>
       <c r="K2" t="n">
-        <v>3.382373013861524</v>
+        <v>3.382418162625982</v>
       </c>
       <c r="L2" t="n">
         <v>7220</v>
       </c>
       <c r="M2" t="n">
-        <v>7100.892033747257</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="N2" t="n">
-        <v>1.124090607251209e-23</v>
+        <v>1.093531298363936e-23</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04209890969082612</v>
+        <v>-0.0405928052277169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,37 +591,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04324539512942533</v>
+        <v>0.04219295914182774</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1268583266417037</v>
+        <v>-0.1232894855468693</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0426605072600514</v>
+        <v>0.04210387509143549</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3303104023814746</v>
+        <v>0.3360117637295972</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.05997144174729338</v>
+        <v>-0.06073443341649937</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.754357302129628</v>
+        <v>-1.775147039486122</v>
       </c>
       <c r="J3" t="n">
-        <v>3.135473524878675</v>
+        <v>3.134720965027061</v>
       </c>
       <c r="K3" t="n">
-        <v>3.191463192440026</v>
+        <v>3.191372519831829</v>
       </c>
       <c r="L3" t="n">
         <v>7220</v>
       </c>
       <c r="M3" t="n">
-        <v>7100.892033747257</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3303104023814746</v>
+        <v>0.3360117637295972</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2292296347053535</v>
+        <v>0.230026785190034</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,37 +648,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04162304148607206</v>
+        <v>0.04275687264023308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1476499724656357</v>
+        <v>0.1462248547236111</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3108092969450713</v>
+        <v>0.3138287156564569</v>
       </c>
       <c r="G4" t="n">
-        <v>3.644258234333755e-08</v>
+        <v>7.453607464503637e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2669028896269001</v>
+        <v>0.2684816016281894</v>
       </c>
       <c r="I4" t="n">
-        <v>9.059053515164027</v>
+        <v>9.109177240226145</v>
       </c>
       <c r="J4" t="n">
-        <v>3.050887376822456</v>
+        <v>3.052316367566833</v>
       </c>
       <c r="K4" t="n">
-        <v>2.797463647892605</v>
+        <v>2.797488208390147</v>
       </c>
       <c r="L4" t="n">
         <v>7220</v>
       </c>
       <c r="M4" t="n">
-        <v>7100.892033747257</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="N4" t="n">
-        <v>5.466387351500632e-08</v>
+        <v>1.118041119675546e-07</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03933933271771812</v>
+        <v>0.0393393327177181</v>
       </c>
       <c r="E2" t="n">
-        <v>0.321436199225089</v>
+        <v>0.3214361992250891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4756435498302205</v>
+        <v>0.4756435498302204</v>
       </c>
       <c r="G2" t="n">
-        <v>4.032349524444008e-24</v>
+        <v>4.032349524443835e-24</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4677085962881634</v>
+        <v>0.4677085962881629</v>
       </c>
       <c r="I2" t="n">
-        <v>11.7036134722028</v>
+        <v>11.70361347220279</v>
       </c>
       <c r="J2" t="n">
         <v>3.778810823675779</v>
@@ -560,7 +560,7 @@
         <v>7095.308361203054</v>
       </c>
       <c r="N2" t="n">
-        <v>1.209704857333202e-23</v>
+        <v>1.209704857333151e-23</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04071597969725242</v>
+        <v>-0.04071597969725245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -597,22 +597,22 @@
         <v>-0.1234163820460073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04198442265150243</v>
+        <v>0.0419844226515024</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3345692469681956</v>
+        <v>0.3345692469681951</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06413795733397988</v>
+        <v>-0.06413795733398085</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.874509212109825</v>
+        <v>-1.874509212109853</v>
       </c>
       <c r="J3" t="n">
         <v>3.131806206400518</v>
       </c>
       <c r="K3" t="n">
-        <v>3.191633673629502</v>
+        <v>3.191633673629503</v>
       </c>
       <c r="L3" t="n">
         <v>7220</v>
@@ -621,7 +621,7 @@
         <v>7093.805668076424</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3345692469681956</v>
+        <v>0.3345692469681951</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2303472064753823</v>
+        <v>0.2303472064753822</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04274619914367981</v>
+        <v>0.04274619914367982</v>
       </c>
       <c r="E4" t="n">
         <v>0.1465661956777929</v>
@@ -657,7 +657,7 @@
         <v>0.3141282172729716</v>
       </c>
       <c r="G4" t="n">
-        <v>7.096210791271779e-08</v>
+        <v>7.096210791271882e-08</v>
       </c>
       <c r="H4" t="n">
         <v>0.2528818070312245</v>
@@ -678,7 +678,7 @@
         <v>7093.528441237814</v>
       </c>
       <c r="N4" t="n">
-        <v>1.064431618690767e-07</v>
+        <v>1.064431618690782e-07</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0393393327177181</v>
+        <v>0.03933933271771813</v>
       </c>
       <c r="E2" t="n">
         <v>0.3214361992250891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4756435498302204</v>
+        <v>0.4756435498302206</v>
       </c>
       <c r="G2" t="n">
-        <v>4.032349524443835e-24</v>
+        <v>4.032349524444008e-24</v>
       </c>
       <c r="H2" t="n">
         <v>0.4677085962881629</v>
@@ -560,7 +560,7 @@
         <v>7095.308361203054</v>
       </c>
       <c r="N2" t="n">
-        <v>1.209704857333151e-23</v>
+        <v>1.209704857333202e-23</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04071597969725245</v>
+        <v>-0.04071597969725241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -597,22 +597,22 @@
         <v>-0.1234163820460073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0419844226515024</v>
+        <v>0.04198442265150244</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3345692469681951</v>
+        <v>0.3345692469681958</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06413795733398085</v>
+        <v>-0.06413795733397942</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.874509212109853</v>
+        <v>-1.874509212109811</v>
       </c>
       <c r="J3" t="n">
         <v>3.131806206400518</v>
       </c>
       <c r="K3" t="n">
-        <v>3.191633673629503</v>
+        <v>3.191633673629502</v>
       </c>
       <c r="L3" t="n">
         <v>7220</v>
@@ -621,7 +621,7 @@
         <v>7093.805668076424</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3345692469681951</v>
+        <v>0.3345692469681958</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2303472064753822</v>
+        <v>0.2303472064753823</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         <v>0.3141282172729716</v>
       </c>
       <c r="G4" t="n">
-        <v>7.096210791271882e-08</v>
+        <v>7.096210791271809e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2528818070312245</v>
+        <v>0.2528818070312249</v>
       </c>
       <c r="I4" t="n">
-        <v>8.576871305907101</v>
+        <v>8.576871305907115</v>
       </c>
       <c r="J4" t="n">
         <v>3.038978091517199</v>
@@ -675,10 +675,10 @@
         <v>7220</v>
       </c>
       <c r="M4" t="n">
-        <v>7093.528441237814</v>
+        <v>7093.528441237813</v>
       </c>
       <c r="N4" t="n">
-        <v>1.064431618690782e-07</v>
+        <v>1.064431618690771e-07</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3642249454799705</v>
+        <v>0.3642249454799706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -533,22 +533,22 @@
         <v>0.03859338896492542</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2885832930673711</v>
+        <v>0.2885832930673712</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4398665978925699</v>
+        <v>0.43986659789257</v>
       </c>
       <c r="G2" t="n">
-        <v>3.817947647451507e-21</v>
+        <v>3.817947647451479e-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4385066466877225</v>
+        <v>0.4385066466877215</v>
       </c>
       <c r="I2" t="n">
-        <v>10.79210990728051</v>
+        <v>10.79210990728049</v>
       </c>
       <c r="J2" t="n">
-        <v>3.766054915857044</v>
+        <v>3.766054915857043</v>
       </c>
       <c r="K2" t="n">
         <v>3.399208588958882</v>
@@ -560,7 +560,7 @@
         <v>6054.814949838281</v>
       </c>
       <c r="N2" t="n">
-        <v>1.145384294235452e-20</v>
+        <v>1.145384294235444e-20</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.003320233432694924</v>
+        <v>-0.003320233432694946</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -600,13 +600,13 @@
         <v>0.09498926063717983</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9472230553604787</v>
+        <v>0.9472230553604783</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0003080184020601404</v>
+        <v>-0.0003080184020606005</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.009354986623808818</v>
+        <v>-0.009354986623822791</v>
       </c>
       <c r="J3" t="n">
         <v>3.177946098060961</v>
@@ -621,7 +621,7 @@
         <v>6055.852863629239</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9472230553604787</v>
+        <v>0.9472230553604783</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1649187804765009</v>
+        <v>0.164918780476501</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04156356015237647</v>
+        <v>0.04156356015237646</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0834556995085789</v>
+        <v>0.08345569950857899</v>
       </c>
       <c r="F4" t="n">
         <v>0.2463818614444229</v>
       </c>
       <c r="G4" t="n">
-        <v>7.251803917655306e-05</v>
+        <v>7.251803917655231e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1560165140786414</v>
+        <v>0.1560165140786419</v>
       </c>
       <c r="I4" t="n">
-        <v>5.329621316165748</v>
+        <v>5.329621316165764</v>
       </c>
       <c r="J4" t="n">
-        <v>2.957435996302532</v>
+        <v>2.957435996302533</v>
       </c>
       <c r="K4" t="n">
         <v>2.807791349999501</v>
@@ -678,7 +678,7 @@
         <v>6055.992193006092</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001087770587648296</v>
+        <v>0.0001087770587648285</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3642249454799706</v>
+        <v>0.3642249454799705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,25 +530,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03859338896492542</v>
+        <v>0.03859338896492541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2885832930673712</v>
+        <v>0.2885832930673711</v>
       </c>
       <c r="F2" t="n">
-        <v>0.43986659789257</v>
+        <v>0.4398665978925698</v>
       </c>
       <c r="G2" t="n">
-        <v>3.817947647451479e-21</v>
+        <v>3.817947647451369e-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4385066466877215</v>
+        <v>0.4385066466877225</v>
       </c>
       <c r="I2" t="n">
-        <v>10.79210990728049</v>
+        <v>10.79210990728051</v>
       </c>
       <c r="J2" t="n">
-        <v>3.766054915857043</v>
+        <v>3.766054915857044</v>
       </c>
       <c r="K2" t="n">
         <v>3.399208588958882</v>
@@ -560,7 +560,7 @@
         <v>6054.814949838281</v>
       </c>
       <c r="N2" t="n">
-        <v>1.145384294235444e-20</v>
+        <v>1.145384294235411e-20</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.003320233432694946</v>
+        <v>-0.003320233432695046</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -594,19 +594,19 @@
         <v>0.05015882681790457</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1016297275025697</v>
+        <v>-0.1016297275025698</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09498926063717983</v>
+        <v>0.0949892606371797</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9472230553604783</v>
+        <v>0.9472230553604767</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0003080184020606005</v>
+        <v>-0.0003080184020601404</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.009354986623822791</v>
+        <v>-0.009354986623808818</v>
       </c>
       <c r="J3" t="n">
         <v>3.177946098060961</v>
@@ -621,7 +621,7 @@
         <v>6055.852863629239</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9472230553604783</v>
+        <v>0.9472230553604767</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.164918780476501</v>
+        <v>0.1649187804765009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -651,19 +651,19 @@
         <v>0.04156356015237646</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08345569950857899</v>
+        <v>0.08345569950857891</v>
       </c>
       <c r="F4" t="n">
         <v>0.2463818614444229</v>
       </c>
       <c r="G4" t="n">
-        <v>7.251803917655231e-05</v>
+        <v>7.251803917655306e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1560165140786419</v>
+        <v>0.1560165140786423</v>
       </c>
       <c r="I4" t="n">
-        <v>5.329621316165764</v>
+        <v>5.32962131616578</v>
       </c>
       <c r="J4" t="n">
         <v>2.957435996302533</v>
@@ -675,10 +675,10 @@
         <v>6217</v>
       </c>
       <c r="M4" t="n">
-        <v>6055.992193006092</v>
+        <v>6055.992193006093</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001087770587648285</v>
+        <v>0.0001087770587648296</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3642249454799706</v>
+        <v>0.3642249454799705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,28 +530,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03859338896492542</v>
+        <v>0.03859338896492541</v>
       </c>
       <c r="E2" t="n">
         <v>0.2885832930673712</v>
       </c>
       <c r="F2" t="n">
-        <v>0.43986659789257</v>
+        <v>0.4398665978925699</v>
       </c>
       <c r="G2" t="n">
         <v>3.817947647451369e-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4385066466877226</v>
+        <v>0.4385066466877219</v>
       </c>
       <c r="I2" t="n">
-        <v>10.79210990728052</v>
+        <v>10.7921099072805</v>
       </c>
       <c r="J2" t="n">
-        <v>3.766054915857043</v>
+        <v>3.766054915857044</v>
       </c>
       <c r="K2" t="n">
-        <v>3.399208588958881</v>
+        <v>3.399208588958882</v>
       </c>
       <c r="L2" t="n">
         <v>6217</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.00332023343269494</v>
+        <v>-0.003320233432694858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0501588268179046</v>
+        <v>0.05015882681790457</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1016297275025698</v>
+        <v>-0.1016297275025696</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09498926063717988</v>
+        <v>0.0949892606371799</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9472230553604785</v>
+        <v>0.9472230553604797</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0003080184020606004</v>
@@ -618,10 +618,10 @@
         <v>6217</v>
       </c>
       <c r="M3" t="n">
-        <v>6055.85286362924</v>
+        <v>6055.852863629239</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9472230553604785</v>
+        <v>0.9472230553604797</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1649187804765009</v>
+        <v>0.1649187804765008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,16 +648,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04156356015237646</v>
+        <v>0.04156356015237647</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08345569950857894</v>
+        <v>0.0834556995085788</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2463818614444229</v>
+        <v>0.2463818614444228</v>
       </c>
       <c r="G4" t="n">
-        <v>7.251803917655267e-05</v>
+        <v>7.251803917655401e-05</v>
       </c>
       <c r="H4" t="n">
         <v>0.1560165140786419</v>
@@ -675,10 +675,10 @@
         <v>6217</v>
       </c>
       <c r="M4" t="n">
-        <v>6055.992193006093</v>
+        <v>6055.992193006092</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000108777058764829</v>
+        <v>0.000108777058764831</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -542,16 +542,16 @@
         <v>3.817947647451479e-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4385066466877242</v>
+        <v>0.4385066466877226</v>
       </c>
       <c r="I2" t="n">
-        <v>10.79210990728055</v>
+        <v>10.79210990728051</v>
       </c>
       <c r="J2" t="n">
         <v>3.766054915857044</v>
       </c>
       <c r="K2" t="n">
-        <v>3.399208588958881</v>
+        <v>3.399208588958882</v>
       </c>
       <c r="L2" t="n">
         <v>6217</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.003320233432694858</v>
+        <v>-0.003320233432694951</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -594,16 +594,16 @@
         <v>0.05015882681790457</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1016297275025696</v>
+        <v>-0.1016297275025697</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0949892606371799</v>
+        <v>0.0949892606371798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9472230553604797</v>
+        <v>0.9472230553604782</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0003080184020606004</v>
+        <v>-0.0003080184020606005</v>
       </c>
       <c r="I3" t="n">
         <v>-0.009354986623822791</v>
@@ -621,7 +621,7 @@
         <v>6055.852863629239</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9472230553604797</v>
+        <v>0.9472230553604782</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -651,19 +651,19 @@
         <v>0.04156356015237647</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08345569950857895</v>
+        <v>0.08345569950857892</v>
       </c>
       <c r="F4" t="n">
         <v>0.2463818614444229</v>
       </c>
       <c r="G4" t="n">
-        <v>7.251803917655267e-05</v>
+        <v>7.251803917655284e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1560165140786423</v>
+        <v>0.1560165140786419</v>
       </c>
       <c r="I4" t="n">
-        <v>5.32962131616578</v>
+        <v>5.329621316165764</v>
       </c>
       <c r="J4" t="n">
         <v>2.957435996302533</v>
@@ -675,10 +675,10 @@
         <v>6217</v>
       </c>
       <c r="M4" t="n">
-        <v>6055.992193006093</v>
+        <v>6055.992193006092</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000108777058764829</v>
+        <v>0.0001087770587648293</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03859338896492542</v>
+        <v>0.03859338896492541</v>
       </c>
       <c r="E2" t="n">
         <v>0.2885832930673712</v>
@@ -542,13 +542,13 @@
         <v>3.817947647451369e-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.438506646687721</v>
+        <v>0.4385066466877225</v>
       </c>
       <c r="I2" t="n">
-        <v>10.79210990728047</v>
+        <v>10.79210990728051</v>
       </c>
       <c r="J2" t="n">
-        <v>3.766054915857043</v>
+        <v>3.766054915857044</v>
       </c>
       <c r="K2" t="n">
         <v>3.399208588958882</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.003320233432694986</v>
+        <v>-0.003320233432695015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,25 +591,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05015882681790459</v>
+        <v>0.05015882681790457</v>
       </c>
       <c r="E3" t="n">
         <v>-0.1016297275025698</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09498926063717981</v>
+        <v>0.09498926063717975</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9472230553604777</v>
+        <v>0.9472230553604772</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0003080184020606005</v>
+        <v>-0.0003080184020610605</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.009354986623822791</v>
+        <v>-0.009354986623836764</v>
       </c>
       <c r="J3" t="n">
-        <v>3.177946098060961</v>
+        <v>3.17794609806096</v>
       </c>
       <c r="K3" t="n">
         <v>3.17824342230799</v>
@@ -621,7 +621,7 @@
         <v>6055.852863629239</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9472230553604777</v>
+        <v>0.9472230553604772</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1649187804765009</v>
+        <v>0.1649187804765008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,16 +648,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04156356015237647</v>
+        <v>0.04156356015237646</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08345569950857892</v>
+        <v>0.08345569950857885</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2463818614444229</v>
+        <v>0.2463818614444228</v>
       </c>
       <c r="G4" t="n">
-        <v>7.251803917655284e-05</v>
+        <v>7.25180391765534e-05</v>
       </c>
       <c r="H4" t="n">
         <v>0.1560165140786419</v>
@@ -678,7 +678,7 @@
         <v>6055.992193006092</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001087770587648293</v>
+        <v>0.0001087770587648301</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3642249454799705</v>
+        <v>0.3975380272033305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03859338896492541</v>
+        <v>0.0384345990913346</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2885832930673712</v>
+        <v>0.3222075972240788</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4398665978925699</v>
+        <v>0.4728684571825822</v>
       </c>
       <c r="G2" t="n">
-        <v>3.817947647451369e-21</v>
+        <v>4.491231826565436e-25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4385066466877225</v>
+        <v>0.4731872093428426</v>
       </c>
       <c r="I2" t="n">
-        <v>10.79210990728051</v>
+        <v>11.74941746144693</v>
       </c>
       <c r="J2" t="n">
-        <v>3.766054915857044</v>
+        <v>3.798232017046069</v>
       </c>
       <c r="K2" t="n">
-        <v>3.399208588958882</v>
+        <v>3.398883057584119</v>
       </c>
       <c r="L2" t="n">
-        <v>6217</v>
+        <v>6044</v>
       </c>
       <c r="M2" t="n">
-        <v>6054.814949838281</v>
+        <v>5880.843365300834</v>
       </c>
       <c r="N2" t="n">
-        <v>1.145384294235411e-20</v>
+        <v>1.347369547969631e-24</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.003320233432695015</v>
+        <v>-0.008532607932754623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,37 +591,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05015882681790457</v>
+        <v>0.04743349094085852</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1016297275025698</v>
+        <v>-0.1015005418378443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09498926063717975</v>
+        <v>0.08443532597233501</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9472230553604772</v>
+        <v>0.8572422817678185</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0003080184020610605</v>
+        <v>-0.005388060806230791</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.009354986623836764</v>
+        <v>-0.1636304585650961</v>
       </c>
       <c r="J3" t="n">
-        <v>3.17794609806096</v>
+        <v>3.17353102488338</v>
       </c>
       <c r="K3" t="n">
-        <v>3.17824342230799</v>
+        <v>3.178732399284887</v>
       </c>
       <c r="L3" t="n">
-        <v>6217</v>
+        <v>6044</v>
       </c>
       <c r="M3" t="n">
-        <v>6055.852863629239</v>
+        <v>5880.506490622341</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9472230553604772</v>
+        <v>0.8572422817678185</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1649187804765008</v>
+        <v>0.1731458137302275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,37 +648,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04156356015237646</v>
+        <v>0.0454521769388852</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08345569950857885</v>
+        <v>0.08406118391107048</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2463818614444228</v>
+        <v>0.2622304435493845</v>
       </c>
       <c r="G4" t="n">
-        <v>7.25180391765534e-05</v>
+        <v>0.0001393008282982219</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1560165140786419</v>
+        <v>0.1635443486967275</v>
       </c>
       <c r="I4" t="n">
-        <v>5.329621316165764</v>
+        <v>5.575640438035069</v>
       </c>
       <c r="J4" t="n">
-        <v>2.957435996302533</v>
+        <v>2.964674710289834</v>
       </c>
       <c r="K4" t="n">
-        <v>2.807791349999501</v>
+        <v>2.80810487910786</v>
       </c>
       <c r="L4" t="n">
-        <v>6217</v>
+        <v>6044</v>
       </c>
       <c r="M4" t="n">
-        <v>6055.992193006092</v>
+        <v>5880.104841727702</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001087770587648301</v>
+        <v>0.0002089512424473329</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0384345990913346</v>
+        <v>0.03843459909133461</v>
       </c>
       <c r="E2" t="n">
         <v>0.3222075972240788</v>
@@ -539,16 +539,16 @@
         <v>0.4728684571825822</v>
       </c>
       <c r="G2" t="n">
-        <v>4.491231826565436e-25</v>
+        <v>4.491231826565502e-25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4731872093428426</v>
+        <v>0.473187209342842</v>
       </c>
       <c r="I2" t="n">
-        <v>11.74941746144693</v>
+        <v>11.74941746144692</v>
       </c>
       <c r="J2" t="n">
-        <v>3.798232017046069</v>
+        <v>3.798232017046068</v>
       </c>
       <c r="K2" t="n">
         <v>3.398883057584119</v>
@@ -560,7 +560,7 @@
         <v>5880.843365300834</v>
       </c>
       <c r="N2" t="n">
-        <v>1.347369547969631e-24</v>
+        <v>1.347369547969651e-24</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.008532607932754623</v>
+        <v>-0.008532607932754597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04743349094085852</v>
+        <v>0.0474334909408585</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1015005418378443</v>
+        <v>-0.1015005418378442</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08443532597233501</v>
+        <v>0.08443532597233498</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8572422817678185</v>
+        <v>0.8572422817678189</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.005388060806230791</v>
+        <v>-0.00538806080623125</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1636304585650961</v>
+        <v>-0.16363045856511</v>
       </c>
       <c r="J3" t="n">
         <v>3.17353102488338</v>
@@ -621,7 +621,7 @@
         <v>5880.506490622341</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8572422817678185</v>
+        <v>0.8572422817678189</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0454521769388852</v>
+        <v>0.04545217693888522</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08406118391107048</v>
+        <v>0.08406118391107047</v>
       </c>
       <c r="F4" t="n">
         <v>0.2622304435493845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001393008282982219</v>
+        <v>0.0001393008282982229</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1635443486967275</v>
+        <v>0.163544348696728</v>
       </c>
       <c r="I4" t="n">
-        <v>5.575640438035069</v>
+        <v>5.575640438035085</v>
       </c>
       <c r="J4" t="n">
         <v>2.964674710289834</v>
@@ -675,10 +675,10 @@
         <v>6044</v>
       </c>
       <c r="M4" t="n">
-        <v>5880.104841727702</v>
+        <v>5880.104841727701</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0002089512424473329</v>
+        <v>0.0002089512424473344</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -539,16 +539,16 @@
         <v>0.4728684571825822</v>
       </c>
       <c r="G2" t="n">
-        <v>4.491231826565693e-25</v>
+        <v>4.491231826565629e-25</v>
       </c>
       <c r="H2" t="n">
         <v>0.473187209342842</v>
       </c>
       <c r="I2" t="n">
-        <v>11.74941746144691</v>
+        <v>11.74941746144692</v>
       </c>
       <c r="J2" t="n">
-        <v>3.798232017046069</v>
+        <v>3.798232017046068</v>
       </c>
       <c r="K2" t="n">
         <v>3.398883057584119</v>
@@ -560,7 +560,7 @@
         <v>5880.843365300834</v>
       </c>
       <c r="N2" t="n">
-        <v>1.347369547969708e-24</v>
+        <v>1.347369547969689e-24</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.008532607932754718</v>
+        <v>-0.008532607932754725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,25 +591,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04743349094085851</v>
+        <v>0.04743349094085852</v>
       </c>
       <c r="E3" t="n">
         <v>-0.1015005418378443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08443532597233488</v>
+        <v>0.08443532597233491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8572422817678169</v>
+        <v>0.8572422817678168</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.005388060806230331</v>
+        <v>-0.005388060806230791</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1636304585650821</v>
+        <v>-0.1636304585650961</v>
       </c>
       <c r="J3" t="n">
-        <v>3.173531024883381</v>
+        <v>3.17353102488338</v>
       </c>
       <c r="K3" t="n">
         <v>3.178732399284887</v>
@@ -621,7 +621,7 @@
         <v>5880.506490622341</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8572422817678169</v>
+        <v>0.8572422817678168</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1731458137302275</v>
+        <v>0.1731458137302273</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -651,22 +651,22 @@
         <v>0.0454521769388852</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08406118391107047</v>
+        <v>0.0840611839110703</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2622304435493845</v>
+        <v>0.2622304435493843</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001393008282982222</v>
+        <v>0.0001393008282982244</v>
       </c>
       <c r="H4" t="n">
-        <v>0.163544348696727</v>
+        <v>0.163544348696728</v>
       </c>
       <c r="I4" t="n">
-        <v>5.575640438035053</v>
+        <v>5.575640438035085</v>
       </c>
       <c r="J4" t="n">
-        <v>2.964674710289833</v>
+        <v>2.964674710289834</v>
       </c>
       <c r="K4" t="n">
         <v>2.80810487910786</v>
@@ -678,7 +678,7 @@
         <v>5880.104841727701</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0002089512424473333</v>
+        <v>0.0002089512424473366</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03843459909133461</v>
+        <v>0.03843459909133462</v>
       </c>
       <c r="E2" t="n">
         <v>0.3222075972240788</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4728684571825822</v>
+        <v>0.4728684571825823</v>
       </c>
       <c r="G2" t="n">
-        <v>4.491231826565629e-25</v>
+        <v>4.491231826565693e-25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.473187209342842</v>
+        <v>0.4731872093428421</v>
       </c>
       <c r="I2" t="n">
         <v>11.74941746144692</v>
@@ -560,7 +560,7 @@
         <v>5880.843365300834</v>
       </c>
       <c r="N2" t="n">
-        <v>1.347369547969689e-24</v>
+        <v>1.347369547969708e-24</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.008532607932754725</v>
+        <v>-0.008532607932754689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04743349094085852</v>
+        <v>0.0474334909408585</v>
       </c>
       <c r="E3" t="n">
         <v>-0.1015005418378443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08443532597233491</v>
+        <v>0.08443532597233488</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8572422817678168</v>
+        <v>0.8572422817678174</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.005388060806230791</v>
+        <v>-0.00538806080623125</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1636304585650961</v>
+        <v>-0.16363045856511</v>
       </c>
       <c r="J3" t="n">
         <v>3.17353102488338</v>
@@ -621,7 +621,7 @@
         <v>5880.506490622341</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8572422817678168</v>
+        <v>0.8572422817678174</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1731458137302273</v>
+        <v>0.1731458137302275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -651,13 +651,13 @@
         <v>0.0454521769388852</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0840611839110703</v>
+        <v>0.08406118391107047</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2622304435493843</v>
+        <v>0.2622304435493845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001393008282982244</v>
+        <v>0.0001393008282982222</v>
       </c>
       <c r="H4" t="n">
         <v>0.163544348696728</v>
@@ -678,7 +678,7 @@
         <v>5880.104841727701</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0002089512424473366</v>
+        <v>0.0002089512424473333</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3975380272033306</v>
+        <v>0.3975380272033305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,25 +530,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03843459909133459</v>
+        <v>0.03843459909133462</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3222075972240789</v>
+        <v>0.3222075972240788</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4728684571825823</v>
+        <v>0.4728684571825822</v>
       </c>
       <c r="G2" t="n">
-        <v>4.491231826565276e-25</v>
+        <v>4.491231826565724e-25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4731872093428426</v>
+        <v>0.4731872093428416</v>
       </c>
       <c r="I2" t="n">
-        <v>11.74941746144693</v>
+        <v>11.7494174614469</v>
       </c>
       <c r="J2" t="n">
-        <v>3.798232017046069</v>
+        <v>3.798232017046068</v>
       </c>
       <c r="K2" t="n">
         <v>3.398883057584119</v>
@@ -560,7 +560,7 @@
         <v>5880.843365300834</v>
       </c>
       <c r="N2" t="n">
-        <v>1.347369547969583e-24</v>
+        <v>1.347369547969717e-24</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.008532607932754567</v>
+        <v>-0.008532607932754671</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04743349094085852</v>
+        <v>0.0474334909408585</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1015005418378442</v>
+        <v>-0.1015005418378443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08443532597233505</v>
+        <v>0.0844353259723349</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8572422817678194</v>
+        <v>0.8572422817678176</v>
       </c>
       <c r="H3" t="n">
         <v>-0.005388060806230791</v>
@@ -621,7 +621,7 @@
         <v>5880.506490622341</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8572422817678194</v>
+        <v>0.8572422817678176</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -660,10 +660,10 @@
         <v>0.0001393008282982229</v>
       </c>
       <c r="H4" t="n">
-        <v>0.163544348696728</v>
+        <v>0.1635443486967275</v>
       </c>
       <c r="I4" t="n">
-        <v>5.575640438035085</v>
+        <v>5.575640438035069</v>
       </c>
       <c r="J4" t="n">
         <v>2.964674710289834</v>
